--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260701.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>1,892,321</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,892,321</t>
+          <t>310,672</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>151,499</t>
+          <t>573,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>573,000</t>
+          <t>151,499</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>801,897</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,818,000</t>
+          <t>1,186,441</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,186,441</t>
+          <t>1,818,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>801,897</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>928,659</t>
+          <t>10,513,121</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,513,121</t>
+          <t>928,659</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>493,000</t>
+          <t>4,417,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,417,578</t>
+          <t>493,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,451,981</t>
+          <t>2,575,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2,575,703</t>
+          <t>3,451,981</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>798,000</t>
+          <t>4,918,956</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,918,956</t>
+          <t>1,175,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,175,076</t>
+          <t>798,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,547,400</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>1,547,400</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>995,121</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,743,000</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>1,743,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>995,121</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>252,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>252,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
